--- a/dataset/Non-Faulty/func_pointer.xlsx
+++ b/dataset/Non-Faulty/func_pointer.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,19 +561,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>long ** func_pointer_005_doubleptr_gbl; int global_set=0; float ** func_pointer_006_doubleptr_gbl=NULL; extern volatile int vflag; void func_pointer_006() { int flag=0,i,j; if(func_pointer_006_func_001(flag)==0) { float **(*fptr)(); fptr = func_pointer_006_func_002; func_pointer_006_doubleptr_gbl = fptr();/*Tool should not detect this line as error*/ /*No ERROR:Bad function pointer casting*/ fptr = func_pointer_006_func_003; func_pointer_006_doubleptr_gbl = fptr(); for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { func_pointer_006_doubleptr_gbl[i][j] += 1; } } fptr = func_pointer_006_func_004; func_pointer_006_doubleptr_gbl = fptr(); } } float ** func_pointer_006_func_002() { int i,j; func_pointer_006_doubleptr_gbl=(float **) malloc(10*sizeof(float*)); for(i=0;i&lt;10;i++) { func_pointer_006_doubleptr_gbl[i]=(float *) malloc(10*sizeof(float)); } for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { func_pointer_006_doubleptr_gbl[i][j]=i; } } return func_pointer_006_doubleptr_gbl; } float ** func_pointer_006_func_004() { int i; for(i=0;i&lt;10;i++) { free (func_pointer_006_doubleptr_gbl[i]); func_pointer_006_doubleptr_gbl[i] = NULL; } free(func_pointer_006_doubleptr_gbl); func_pointer_006_doubleptr_gbl = NULL; return func_pointer_006_doubleptr_gbl; } int func_pointer_006_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; } float ** func_pointer_006_func_003() { int i,j; for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { func_pointer_006_doubleptr_gbl[i][j]=i; } } return func_pointer_006_doubleptr_gbl; }</t>
+          <t>long ** func_pointer_005_doubleptr_gbl; int global_set=0; float ** func_pointer_006_doubleptr_gbl=NULL; extern volatile int vflag; void func_pointer_006() { int flag=0,i,j; if(func_pointer_006_func_001(flag)==0) { float **(*fptr)(); fptr = func_pointer_006_func_002; func_pointer_006_doubleptr_gbl = fptr();/*Tool should not detect this line as error*/ /*No ERROR:Bad function pointer casting*/ fptr = func_pointer_006_func_003; func_pointer_006_doubleptr_gbl = fptr(); for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { func_pointer_006_doubleptr_gbl[i][j] += 1; } } fptr = func_pointer_006_func_004; func_pointer_006_doubleptr_gbl = fptr(); } } float ** func_pointer_006_func_003() { int i,j; for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { func_pointer_006_doubleptr_gbl[i][j]=i; } } return func_pointer_006_doubleptr_gbl; } float ** func_pointer_006_func_004() { int i; for(i=0;i&lt;10;i++) { free (func_pointer_006_doubleptr_gbl[i]); func_pointer_006_doubleptr_gbl[i] = NULL; } free(func_pointer_006_doubleptr_gbl); func_pointer_006_doubleptr_gbl = NULL; return func_pointer_006_doubleptr_gbl; } float ** func_pointer_006_func_002() { int i,j; func_pointer_006_doubleptr_gbl=(float **) malloc(10*sizeof(float*)); for(i=0;i&lt;10;i++) { func_pointer_006_doubleptr_gbl[i]=(float *) malloc(10*sizeof(float)); } for(i=0;i&lt;10;i++) { for(j=0;j&lt;10;j++) { func_pointer_006_doubleptr_gbl[i][j]=i; } } return func_pointer_006_doubleptr_gbl; } int func_pointer_006_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; }</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,14 +588,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -610,14 +610,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -632,14 +632,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -654,14 +654,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -676,14 +676,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>itc-benchmarks/02.wo_Defects/func_pointer.c</t>
+          <t>dataset/itc-benchmarks/02.wo_Defects/func_pointer.c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>#define MAX 10 #define MAX 10 typedef struct { int arr[MAX]; int a; int b; int c; } func_pointer_015_s_001; long ** func_pointer_005_doubleptr_gbl; int global_set=0; float ** func_pointer_006_doubleptr_gbl=NULL; extern volatile int vflag; void func_pointer_015 () { func_pointer_015_s_001 st,*st1; st1 = (func_pointer_015_s_001 *)malloc(1*sizeof(func_pointer_015_s_001)); memset(st1, 0, sizeof(*st1)); fptr_gbl = func_pointer_015_func_001; fptr_gbl(&amp;st); void (*fptr3)(func_pointer_015_s_001* st1); fptr3 = func_pointer_015_func_004; fptr3(st1); } void func_pointer_015_func_001(func_pointer_015_s_001* st) { memset(st, 0, sizeof(*st)); st-&gt;a = 1; global_set = 1; } void func_pointer_015_func_004(func_pointer_015_s_001* st1) { if (global_set == MAX) { fptr1_gbl = func_pointer_015_func_002; fptr1_gbl(st1); } else { fptr2_gbl = func_pointer_015_func_003; fptr2_gbl(st1);/*Tool should not detect this line as error*/ /*No ERROR:Bad function pointer casting*/ } } void func_pointer_015_func_002(func_pointer_015_s_001* st1) { int temp=0; int i; for (i = 0; i &lt; MAX; i++) { st1-&gt;arr[i] += i; temp += st1-&gt;arr[i]; } } void func_pointer_015_func_003(func_pointer_015_s_001 *st) { st-&gt;b = st-&gt;c; }</t>
+          <t>#define MAX 10 #define MAX 10 typedef struct { int arr[MAX]; int a; int b; int c; } func_pointer_015_s_001; long ** func_pointer_005_doubleptr_gbl; int global_set=0; float ** func_pointer_006_doubleptr_gbl=NULL; extern volatile int vflag; void func_pointer_015 () { func_pointer_015_s_001 st,*st1; st1 = (func_pointer_015_s_001 *)malloc(1*sizeof(func_pointer_015_s_001)); memset(st1, 0, sizeof(*st1)); fptr_gbl = func_pointer_015_func_001; fptr_gbl(&amp;st); void (*fptr3)(func_pointer_015_s_001* st1); fptr3 = func_pointer_015_func_004; fptr3(st1); } void func_pointer_015_func_001(func_pointer_015_s_001* st) { memset(st, 0, sizeof(*st)); st-&gt;a = 1; global_set = 1; } void func_pointer_015_func_004(func_pointer_015_s_001* st1) { if (global_set == MAX) { fptr1_gbl = func_pointer_015_func_002; fptr1_gbl(st1); } else { fptr2_gbl = func_pointer_015_func_003; fptr2_gbl(st1);/*Tool should not detect this line as error*/ /*No ERROR:Bad function pointer casting*/ } } void func_pointer_015_func_003(func_pointer_015_s_001 *st) { st-&gt;b = st-&gt;c; } void func_pointer_015_func_002(func_pointer_015_s_001* st1) { int temp=0; int i; for (i = 0; i &lt; MAX; i++) { st1-&gt;arr[i] += i; temp += st1-&gt;arr[i]; } }</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Non-Faulty</t>
+          <t>non-faulty</t>
         </is>
       </c>
     </row>
